--- a/artfynd/A 64098-2023 artfynd.xlsx
+++ b/artfynd/A 64098-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64098-2023 artfynd.xlsx
+++ b/artfynd/A 64098-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87903799</v>
+        <v>87902293</v>
       </c>
       <c r="B2" t="n">
-        <v>41405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>42106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652652.9344546281</v>
+        <v>652653</v>
       </c>
       <c r="R2" t="n">
-        <v>6594855.972193664</v>
+        <v>6594856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2020-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
